--- a/Stats Sheet/Round Gaps/Generational.xlsx
+++ b/Stats Sheet/Round Gaps/Generational.xlsx
@@ -238,7 +238,7 @@
     <x:t>Seabasstian</x:t>
   </x:si>
   <x:si>
-    <x:t>tonylmao</x:t>
+    <x:t>Tonylmao</x:t>
   </x:si>
   <x:si>
     <x:t>Valnius</x:t>
